--- a/dcf/MSFT.xlsx
+++ b/dcf/MSFT.xlsx
@@ -915,7 +915,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1171,51 +1171,51 @@
         </is>
       </c>
       <c r="B4" s="53" t="n">
-        <v>0.0762407427437941</v>
+        <v>0.07624804803872437</v>
       </c>
       <c r="C4" s="53" t="n">
-        <v>0.0812407427437941</v>
+        <v>0.08124804803872437</v>
       </c>
       <c r="D4" s="53" t="n">
-        <v>0.08624074274379409</v>
+        <v>0.08624804803872436</v>
       </c>
       <c r="E4" s="53" t="n">
-        <v>0.0912407427437941</v>
+        <v>0.09124804803872437</v>
       </c>
       <c r="F4" s="53" t="n">
-        <v>0.0962407427437941</v>
+        <v>0.09624804803872437</v>
       </c>
       <c r="G4" s="53" t="n">
-        <v>0.1012407427437941</v>
+        <v>0.1012480480387244</v>
       </c>
       <c r="H4" s="53" t="n">
-        <v>0.1062407427437941</v>
+        <v>0.1062480480387244</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="54" t="n">
         <v>9</v>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>452.5480848724027</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>435.051671738573</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>418.3707093037397</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>402.4627724425263</v>
+      <c r="B5" s="55" t="n">
+        <v>388.0757974417112</v>
+      </c>
+      <c r="C5" s="55" t="n">
+        <v>373.3237244395592</v>
+      </c>
+      <c r="D5" s="55" t="n">
+        <v>359.2557553529967</v>
+      </c>
+      <c r="E5" s="55" t="n">
+        <v>345.8363782764721</v>
       </c>
       <c r="F5" s="55" t="n">
-        <v>387.2878463538759</v>
+        <v>333.0320964728473</v>
       </c>
       <c r="G5" s="55" t="n">
-        <v>372.8081787521715</v>
+        <v>320.8113048832084</v>
       </c>
       <c r="H5" s="55" t="n">
-        <v>358.9881417661969</v>
+        <v>309.144174743684</v>
       </c>
     </row>
     <row r="6">
@@ -1223,25 +1223,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>484.7762034416771</v>
+        <v>414.9546636235425</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>465.8200934889218</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>447.7518301137108</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>430.525088831041</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>414.0961819881474</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>398.4238968492464</v>
+        <v>398.9851836608552</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>383.7601863614758</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <v>369.2409077437372</v>
+      </c>
+      <c r="F6" s="55" t="n">
+        <v>355.3907879013481</v>
+      </c>
+      <c r="G6" s="55" t="n">
+        <v>342.1753357486025</v>
       </c>
       <c r="H6" s="55" t="n">
-        <v>383.4693443252008</v>
+        <v>329.5620026541086</v>
       </c>
     </row>
     <row r="7">
@@ -1249,25 +1249,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>517.0043220109515</v>
+        <v>441.8335298053738</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>496.5885152392705</v>
+        <v>424.6466428821511</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>477.1329509236818</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>458.5874052195558</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>440.9045176224188</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>424.0396149463213</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>407.9505468842048</v>
+        <v>408.2646173699549</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>392.6454372110023</v>
+      </c>
+      <c r="F7" s="55" t="n">
+        <v>377.7494793298489</v>
+      </c>
+      <c r="G7" s="55" t="n">
+        <v>363.5393666139967</v>
+      </c>
+      <c r="H7" s="55" t="n">
+        <v>349.9798305645331</v>
       </c>
     </row>
     <row r="8">
@@ -1275,25 +1275,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>549.2324405802258</v>
+        <v>468.712395987205</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>527.3569369896193</v>
+        <v>450.3081021034471</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>506.5140717336529</v>
+        <v>432.7690483784341</v>
       </c>
       <c r="E8" s="56" t="n">
-        <v>486.6497216080705</v>
+        <v>416.0499666782675</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>467.7128532566902</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>449.655333043396</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>432.4317494432088</v>
+        <v>400.1081707583497</v>
+      </c>
+      <c r="G8" s="55" t="n">
+        <v>384.9033974793908</v>
+      </c>
+      <c r="H8" s="55" t="n">
+        <v>370.3976584749577</v>
       </c>
     </row>
     <row r="9">
@@ -1301,25 +1301,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>581.4605591495</v>
+        <v>495.5912621690363</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>558.125358739968</v>
+        <v>475.969561324743</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>535.895192543624</v>
+        <v>457.2734793869133</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>514.7120379965852</v>
+        <v>439.4544961455326</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>494.5211888909616</v>
+        <v>422.4668621868505</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>475.2710511404709</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>456.9129520022127</v>
+        <v>406.2674283447851</v>
+      </c>
+      <c r="H9" s="55" t="n">
+        <v>390.8154863853823</v>
       </c>
     </row>
     <row r="10">
@@ -1327,25 +1327,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>613.6886777187743</v>
+        <v>522.4701283508676</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>588.8937804903167</v>
+        <v>501.631020546039</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>565.2763133535951</v>
+        <v>481.7779103953924</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>542.7743543850999</v>
+        <v>462.8590256127977</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>521.329524525233</v>
+        <v>444.8255536153513</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>500.8867692375457</v>
+        <v>427.6314592101792</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>481.3941545612166</v>
+        <v>411.2333142958068</v>
       </c>
     </row>
     <row r="11">
@@ -1353,25 +1353,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>645.9167962880488</v>
+        <v>549.3489945326988</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>619.6622022406656</v>
+        <v>527.292479767335</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>594.6574341635661</v>
+        <v>506.2823414038716</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>570.8366707736146</v>
+        <v>486.2635550800629</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>548.1378601595044</v>
+        <v>467.1842450438521</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>526.5024873346206</v>
+        <v>448.9954900755733</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>505.8753571202206</v>
+        <v>431.6511422062313</v>
       </c>
     </row>
     <row r="13">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="B13" s="55" t="n">
-        <v>390.489990234375</v>
+        <v>393.5849914550781</v>
       </c>
     </row>
     <row r="14">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="B14" s="57" t="n">
-        <v>0.0912407427437941</v>
+        <v>0.09124804803872437</v>
       </c>
       <c r="C14" s="58" t="n">
         <v>12</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="I8" s="50" t="n">
-        <v>0.9872005737829918</v>
+        <v>0.9890629546802014</v>
       </c>
       <c r="K8" s="27">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24597,7 +24597,7 @@
         </is>
       </c>
       <c r="B48" s="25" t="n">
-        <v>390.489990234375</v>
+        <v>393.5849914550781</v>
       </c>
     </row>
     <row r="49">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="B49" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="B58" s="30" t="n">
-        <v>486.6497216080705</v>
+        <v>416.0499666782675</v>
       </c>
       <c r="C58" s="30" t="n">
-        <v>660.812361609262</v>
+        <v>551.1785122220725</v>
       </c>
       <c r="D58" s="30" t="n">
-        <v>353.4506594863411</v>
+        <v>309.8911055327284</v>
       </c>
     </row>
     <row r="59">
